--- a/chapters/08/core/AIHE-B05/supp/AIHE-EX15/xlsx/AIHE-EX15_workbook.xlsx
+++ b/chapters/08/core/AIHE-B05/supp/AIHE-EX15/xlsx/AIHE-EX15_workbook.xlsx
@@ -84,12 +84,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -105,10 +105,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,10 +116,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -139,7 +139,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -147,7 +147,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -603,12 +603,12 @@
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>Patients, clinicians, organizations, and adaptive behavior</t>
+          <t>Patients, clinicians, organizations, and adaptive behaviour</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>Do interactions and behavioral rules drive outcomes?</t>
+          <t>Do interactions and behavioural rules drive outcomes?</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
